--- a/data/raw/comparaisons/fiches_excell.xlsx
+++ b/data/raw/comparaisons/fiches_excell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPF\STAGE ACCESS\Code\Prototype_Appli_DefisAccess\data\raw\comparaisons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E11DAB7-9A3A-4DD2-B4DA-18F072963E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00077E96-4534-4546-90E1-5CC60BE8BE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="588" yWindow="180" windowWidth="21912" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="588" yWindow="0" windowWidth="21912" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="294">
   <si>
     <t>equipe</t>
   </si>
@@ -1215,22 +1215,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.19921875" customWidth="1"/>
     <col min="2" max="2" width="30.09765625" customWidth="1"/>
     <col min="3" max="3" width="23.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" customWidth="1"/>
-    <col min="6" max="6" width="19.09765625" customWidth="1"/>
-    <col min="7" max="7" width="12.59765625" customWidth="1"/>
-    <col min="8" max="8" width="12.09765625" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="26" width="7.59765625" customWidth="1"/>
+    <col min="5" max="6" width="10.69921875" customWidth="1"/>
+    <col min="7" max="7" width="19.09765625" customWidth="1"/>
+    <col min="8" max="8" width="12.59765625" customWidth="1"/>
+    <col min="9" max="9" width="12.09765625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="27" width="7.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1247,19 +1247,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1275,8 +1278,9 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1292,8 +1296,9 @@
       <c r="E3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1309,8 +1314,9 @@
       <c r="E4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1326,8 +1332,9 @@
       <c r="E5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1343,8 +1350,9 @@
       <c r="E6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1360,8 +1368,9 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1377,8 +1386,9 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1394,8 +1404,9 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -1411,8 +1422,9 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1428,8 +1440,9 @@
       <c r="E11" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1445,8 +1458,9 @@
       <c r="E12" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1462,8 +1476,9 @@
       <c r="E13" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -1479,8 +1494,9 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1496,8 +1512,9 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1513,8 +1530,9 @@
       <c r="E16" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -1530,8 +1548,9 @@
       <c r="E17" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -1547,8 +1566,9 @@
       <c r="E18" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -1564,8 +1584,9 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1581,8 +1602,9 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -1598,8 +1620,9 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -1615,8 +1638,9 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -1632,8 +1656,9 @@
       <c r="E23" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1649,8 +1674,9 @@
       <c r="E24" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -1666,8 +1692,9 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -1683,8 +1710,9 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -1700,8 +1728,9 @@
       <c r="E27" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -1717,8 +1746,9 @@
       <c r="E28" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1734,8 +1764,9 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -1751,8 +1782,9 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -1768,8 +1800,9 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1785,8 +1818,9 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -1802,8 +1836,9 @@
       <c r="E33" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -1819,8 +1854,9 @@
       <c r="E34" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -1836,8 +1872,9 @@
       <c r="E35" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1853,8 +1890,9 @@
       <c r="E36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -1870,8 +1908,9 @@
       <c r="E37" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1887,8 +1926,9 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -1904,8 +1944,9 @@
       <c r="E39" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1921,8 +1962,9 @@
       <c r="E40" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>1</v>
       </c>
@@ -1938,8 +1980,9 @@
       <c r="E41" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -1955,8 +1998,9 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>1</v>
       </c>
@@ -1972,8 +2016,9 @@
       <c r="E43" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -1989,8 +2034,9 @@
       <c r="E44" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>1</v>
       </c>
@@ -2006,8 +2052,9 @@
       <c r="E45" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -2023,8 +2070,9 @@
       <c r="E46" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -2040,8 +2088,9 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>1</v>
       </c>
@@ -2057,8 +2106,9 @@
       <c r="E48" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -2074,8 +2124,9 @@
       <c r="E49" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -2091,8 +2142,9 @@
       <c r="E50" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -2108,8 +2160,9 @@
       <c r="E51" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -2125,8 +2178,9 @@
       <c r="E52" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>1</v>
       </c>
@@ -2142,8 +2196,9 @@
       <c r="E53" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>1</v>
       </c>
@@ -2159,8 +2214,9 @@
       <c r="E54" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>1</v>
       </c>
@@ -2176,8 +2232,9 @@
       <c r="E55" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>1</v>
       </c>
@@ -2193,8 +2250,9 @@
       <c r="E56" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>1</v>
       </c>
@@ -2210,8 +2268,9 @@
       <c r="E57" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>1</v>
       </c>
@@ -2227,8 +2286,9 @@
       <c r="E58" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>1</v>
       </c>
@@ -2244,8 +2304,9 @@
       <c r="E59" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>1</v>
       </c>
@@ -2261,8 +2322,9 @@
       <c r="E60" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>1</v>
       </c>
@@ -2278,8 +2340,9 @@
       <c r="E61" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -2295,8 +2358,9 @@
       <c r="E62" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>1</v>
       </c>
@@ -2312,8 +2376,9 @@
       <c r="E63" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>1</v>
       </c>
@@ -2329,8 +2394,9 @@
       <c r="E64" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>1</v>
       </c>
@@ -2346,8 +2412,9 @@
       <c r="E65" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>1</v>
       </c>
@@ -2363,8 +2430,9 @@
       <c r="E66" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>1</v>
       </c>
@@ -2380,8 +2448,9 @@
       <c r="E67" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>1</v>
       </c>
@@ -2397,8 +2466,9 @@
       <c r="E68" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1</v>
       </c>
@@ -2414,8 +2484,9 @@
       <c r="E69" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>1</v>
       </c>
@@ -2431,8 +2502,9 @@
       <c r="E70" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>1</v>
       </c>
@@ -2448,8 +2520,9 @@
       <c r="E71" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>1</v>
       </c>
@@ -2465,8 +2538,9 @@
       <c r="E72" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>1</v>
       </c>
@@ -2482,8 +2556,9 @@
       <c r="E73" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>1</v>
       </c>
@@ -2499,8 +2574,9 @@
       <c r="E74" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>1</v>
       </c>
@@ -2516,8 +2592,9 @@
       <c r="E75" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>1</v>
       </c>
@@ -2533,8 +2610,9 @@
       <c r="E76" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F76" s="1"/>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -2550,8 +2628,9 @@
       <c r="E77" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F77" s="1"/>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1</v>
       </c>
@@ -2567,8 +2646,9 @@
       <c r="E78" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F78" s="1"/>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>1</v>
       </c>
@@ -2584,8 +2664,9 @@
       <c r="E79" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>1</v>
       </c>
@@ -2601,8 +2682,9 @@
       <c r="E80" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>1</v>
       </c>
@@ -2618,8 +2700,9 @@
       <c r="E81" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>1</v>
       </c>
@@ -2635,8 +2718,9 @@
       <c r="E82" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>1</v>
       </c>
@@ -2652,8 +2736,9 @@
       <c r="E83" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>1</v>
       </c>
@@ -2669,8 +2754,9 @@
       <c r="E84" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>1</v>
       </c>
@@ -2686,8 +2772,9 @@
       <c r="E85" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>1</v>
       </c>
@@ -2703,8 +2790,9 @@
       <c r="E86" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>1</v>
       </c>
@@ -2720,8 +2808,9 @@
       <c r="E87" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>1</v>
       </c>
@@ -2737,8 +2826,9 @@
       <c r="E88" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>1</v>
       </c>
@@ -2754,8 +2844,9 @@
       <c r="E89" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>1</v>
       </c>
@@ -2771,8 +2862,9 @@
       <c r="E90" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>1</v>
       </c>
@@ -2788,8 +2880,9 @@
       <c r="E91" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>1</v>
       </c>
@@ -2805,8 +2898,9 @@
       <c r="E92" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>1</v>
       </c>
@@ -2822,8 +2916,9 @@
       <c r="E93" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>1</v>
       </c>
@@ -2839,8 +2934,9 @@
       <c r="E94" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>1</v>
       </c>
@@ -2856,8 +2952,9 @@
       <c r="E95" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>1</v>
       </c>
@@ -2873,8 +2970,9 @@
       <c r="E96" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F96" s="1"/>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>1</v>
       </c>
@@ -2890,8 +2988,9 @@
       <c r="E97" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>1</v>
       </c>
@@ -2907,8 +3006,9 @@
       <c r="E98" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F98" s="1"/>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>1</v>
       </c>
@@ -2924,8 +3024,9 @@
       <c r="E99" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>1</v>
       </c>
@@ -2941,8 +3042,9 @@
       <c r="E100" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>1</v>
       </c>
@@ -2958,8 +3060,9 @@
       <c r="E101" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F101" s="1"/>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>1</v>
       </c>
@@ -2975,8 +3078,9 @@
       <c r="E102" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>1</v>
       </c>
@@ -2992,8 +3096,9 @@
       <c r="E103" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>1</v>
       </c>
@@ -3009,8 +3114,9 @@
       <c r="E104" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F104" s="1"/>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>1</v>
       </c>
@@ -3026,8 +3132,9 @@
       <c r="E105" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F105" s="1"/>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>1</v>
       </c>
@@ -3043,8 +3150,9 @@
       <c r="E106" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>1</v>
       </c>
@@ -3060,8 +3168,9 @@
       <c r="E107" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -3077,8 +3186,9 @@
       <c r="E108" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>1</v>
       </c>
@@ -3094,8 +3204,9 @@
       <c r="E109" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>1</v>
       </c>
@@ -3111,8 +3222,9 @@
       <c r="E110" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>1</v>
       </c>
@@ -3128,8 +3240,9 @@
       <c r="E111" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>1</v>
       </c>
@@ -3145,8 +3258,9 @@
       <c r="E112" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>1</v>
       </c>
@@ -3162,8 +3276,9 @@
       <c r="E113" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>1</v>
       </c>
@@ -3179,8 +3294,9 @@
       <c r="E114" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>1</v>
       </c>
@@ -3196,8 +3312,9 @@
       <c r="E115" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>1</v>
       </c>
@@ -3213,8 +3330,9 @@
       <c r="E116" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F116" s="1"/>
+    </row>
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>1</v>
       </c>
@@ -3230,8 +3348,9 @@
       <c r="E117" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F117" s="1"/>
+    </row>
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>1</v>
       </c>
@@ -3247,8 +3366,9 @@
       <c r="E118" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>1</v>
       </c>
@@ -3264,8 +3384,9 @@
       <c r="E119" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>1</v>
       </c>
@@ -3281,8 +3402,9 @@
       <c r="E120" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F120" s="1"/>
+    </row>
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>1</v>
       </c>
@@ -3298,8 +3420,9 @@
       <c r="E121" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>1</v>
       </c>
@@ -3315,8 +3438,9 @@
       <c r="E122" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F122" s="1"/>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>1</v>
       </c>
@@ -3332,8 +3456,9 @@
       <c r="E123" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F123" s="1"/>
+    </row>
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>1</v>
       </c>
@@ -3349,8 +3474,9 @@
       <c r="E124" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F124" s="1"/>
+    </row>
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>1</v>
       </c>
@@ -3366,8 +3492,9 @@
       <c r="E125" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F125" s="1"/>
+    </row>
+    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>1</v>
       </c>
@@ -3383,8 +3510,9 @@
       <c r="E126" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F126" s="1"/>
+    </row>
+    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>1</v>
       </c>
@@ -3400,8 +3528,9 @@
       <c r="E127" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>1</v>
       </c>
@@ -3417,8 +3546,9 @@
       <c r="E128" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F128" s="1"/>
+    </row>
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>1</v>
       </c>
@@ -3434,8 +3564,9 @@
       <c r="E129" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F129" s="1"/>
+    </row>
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>1</v>
       </c>
@@ -3451,8 +3582,9 @@
       <c r="E130" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F130" s="1"/>
+    </row>
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>1</v>
       </c>
@@ -3468,8 +3600,9 @@
       <c r="E131" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F131" s="1"/>
+    </row>
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>1</v>
       </c>
@@ -3485,8 +3618,9 @@
       <c r="E132" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F132" s="1"/>
+    </row>
+    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>1</v>
       </c>
@@ -3502,8 +3636,9 @@
       <c r="E133" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>1</v>
       </c>
@@ -3519,8 +3654,9 @@
       <c r="E134" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F134" s="1"/>
+    </row>
+    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>1</v>
       </c>
@@ -3536,8 +3672,9 @@
       <c r="E135" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F135" s="1"/>
+    </row>
+    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>1</v>
       </c>
@@ -3553,8 +3690,9 @@
       <c r="E136" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F136" s="1"/>
+    </row>
+    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>1</v>
       </c>
@@ -3570,8 +3708,9 @@
       <c r="E137" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F137" s="1"/>
+    </row>
+    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1</v>
       </c>
@@ -3587,8 +3726,9 @@
       <c r="E138" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F138" s="1"/>
+    </row>
+    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>1</v>
       </c>
@@ -3604,8 +3744,9 @@
       <c r="E139" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F139" s="1"/>
+    </row>
+    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>1</v>
       </c>
@@ -3621,8 +3762,9 @@
       <c r="E140" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F140" s="1"/>
+    </row>
+    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>1</v>
       </c>
@@ -3638,8 +3780,9 @@
       <c r="E141" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F141" s="1"/>
+    </row>
+    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1</v>
       </c>
@@ -3655,8 +3798,9 @@
       <c r="E142" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F142" s="1"/>
+    </row>
+    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>1</v>
       </c>
@@ -3672,8 +3816,9 @@
       <c r="E143" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F143" s="1"/>
+    </row>
+    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>1</v>
       </c>
@@ -3689,8 +3834,9 @@
       <c r="E144" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F144" s="1"/>
+    </row>
+    <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>1</v>
       </c>
@@ -3706,8 +3852,9 @@
       <c r="E145" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F145" s="1"/>
+    </row>
+    <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>1</v>
       </c>
@@ -3723,8 +3870,9 @@
       <c r="E146" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F146" s="1"/>
+    </row>
+    <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>1</v>
       </c>
@@ -3740,8 +3888,9 @@
       <c r="E147" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F147" s="1"/>
+    </row>
+    <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>1</v>
       </c>
@@ -3757,8 +3906,9 @@
       <c r="E148" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F148" s="1"/>
+    </row>
+    <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>1</v>
       </c>
@@ -3774,8 +3924,9 @@
       <c r="E149" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F149" s="1"/>
+    </row>
+    <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>1</v>
       </c>
@@ -3791,8 +3942,9 @@
       <c r="E150" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F150" s="1"/>
+    </row>
+    <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>1</v>
       </c>
@@ -3808,8 +3960,9 @@
       <c r="E151" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F151" s="1"/>
+    </row>
+    <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>1</v>
       </c>
@@ -3825,8 +3978,9 @@
       <c r="E152" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F152" s="1"/>
+    </row>
+    <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>1</v>
       </c>
@@ -3842,8 +3996,9 @@
       <c r="E153" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F153" s="1"/>
+    </row>
+    <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>1</v>
       </c>
@@ -3859,8 +4014,9 @@
       <c r="E154" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F154" s="1"/>
+    </row>
+    <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>1</v>
       </c>
@@ -3876,8 +4032,9 @@
       <c r="E155" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F155" s="1"/>
+    </row>
+    <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>1</v>
       </c>
@@ -3893,8 +4050,9 @@
       <c r="E156" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F156" s="1"/>
+    </row>
+    <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>1</v>
       </c>
@@ -3910,8 +4068,9 @@
       <c r="E157" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F157" s="1"/>
+    </row>
+    <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>1</v>
       </c>
@@ -3927,8 +4086,9 @@
       <c r="E158" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F158" s="1"/>
+    </row>
+    <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>1</v>
       </c>
@@ -3944,8 +4104,9 @@
       <c r="E159" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F159" s="1"/>
+    </row>
+    <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>1</v>
       </c>
@@ -3961,8 +4122,9 @@
       <c r="E160" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F160" s="1"/>
+    </row>
+    <row r="161" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>1</v>
       </c>
@@ -3978,8 +4140,9 @@
       <c r="E161" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F161" s="1"/>
+    </row>
+    <row r="162" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>1</v>
       </c>
@@ -3995,8 +4158,9 @@
       <c r="E162" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F162" s="1"/>
+    </row>
+    <row r="163" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>1</v>
       </c>
@@ -4012,8 +4176,9 @@
       <c r="E163" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F163" s="1"/>
+    </row>
+    <row r="164" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>1</v>
       </c>
@@ -4029,19 +4194,20 @@
       <c r="E164" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F164" s="1"/>
+    </row>
+    <row r="165" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4874,19 +5040,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.59765625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="47.59765625" customWidth="1"/>
-    <col min="4" max="5" width="7.59765625" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" customWidth="1"/>
-    <col min="7" max="7" width="12.8984375" customWidth="1"/>
-    <col min="8" max="26" width="7.59765625" customWidth="1"/>
+    <col min="4" max="6" width="7.59765625" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="8" max="8" width="12.8984375" customWidth="1"/>
+    <col min="9" max="27" width="7.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4903,19 +5069,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -4931,20 +5100,21 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
       <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4960,8 +5130,9 @@
       <c r="E3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4977,8 +5148,9 @@
       <c r="E4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -4994,20 +5166,21 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="1"/>
+      <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -5023,11 +5196,12 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -5043,8 +5217,9 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -5060,8 +5235,9 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -5077,8 +5253,9 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -5094,8 +5271,9 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -5111,8 +5289,9 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -5128,8 +5307,9 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -5145,8 +5325,9 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -5162,8 +5343,9 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -5179,8 +5361,9 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -5196,8 +5379,9 @@
       <c r="E16" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -5213,8 +5397,9 @@
       <c r="E17" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -5230,8 +5415,9 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -5247,8 +5433,9 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -5264,8 +5451,9 @@
       <c r="E20" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -5281,8 +5469,9 @@
       <c r="E21" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -5298,8 +5487,9 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>2</v>
       </c>
@@ -5315,8 +5505,9 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>2</v>
       </c>
@@ -5332,8 +5523,9 @@
       <c r="E24" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -5349,8 +5541,9 @@
       <c r="E25" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>2</v>
       </c>
@@ -5366,8 +5559,9 @@
       <c r="E26" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>2</v>
       </c>
@@ -5383,8 +5577,9 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>2</v>
       </c>
@@ -5400,8 +5595,9 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>2</v>
       </c>
@@ -5417,8 +5613,9 @@
       <c r="E29" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -5434,8 +5631,9 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>2</v>
       </c>
@@ -5451,8 +5649,9 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>2</v>
       </c>
@@ -5468,8 +5667,9 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -5485,8 +5685,9 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>2</v>
       </c>
@@ -5502,8 +5703,9 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2</v>
       </c>
@@ -5519,8 +5721,9 @@
       <c r="E35" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>2</v>
       </c>
@@ -5536,8 +5739,9 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -5553,8 +5757,9 @@
       <c r="E37" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>2</v>
       </c>
@@ -5570,8 +5775,9 @@
       <c r="E38" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -5587,8 +5793,9 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2</v>
       </c>
@@ -5604,8 +5811,9 @@
       <c r="E40" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -5621,8 +5829,9 @@
       <c r="E41" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>2</v>
       </c>
@@ -5638,8 +5847,9 @@
       <c r="E42" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>2</v>
       </c>
@@ -5655,8 +5865,9 @@
       <c r="E43" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>2</v>
       </c>
@@ -5672,8 +5883,9 @@
       <c r="E44" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>2</v>
       </c>
@@ -5689,8 +5901,9 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>2</v>
       </c>
@@ -5706,8 +5919,9 @@
       <c r="E46" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>2</v>
       </c>
@@ -5723,8 +5937,9 @@
       <c r="E47" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>2</v>
       </c>
@@ -5740,8 +5955,9 @@
       <c r="E48" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>2</v>
       </c>
@@ -5757,8 +5973,9 @@
       <c r="E49" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>2</v>
       </c>
@@ -5774,8 +5991,9 @@
       <c r="E50" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>2</v>
       </c>
@@ -5791,8 +6009,9 @@
       <c r="E51" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>2</v>
       </c>
@@ -5808,8 +6027,9 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>2</v>
       </c>
@@ -5825,8 +6045,9 @@
       <c r="E53" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>2</v>
       </c>
@@ -5842,8 +6063,9 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -5859,8 +6081,9 @@
       <c r="E55" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>2</v>
       </c>
@@ -5876,8 +6099,9 @@
       <c r="E56" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>2</v>
       </c>
@@ -5893,8 +6117,9 @@
       <c r="E57" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>2</v>
       </c>
@@ -5910,8 +6135,9 @@
       <c r="E58" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -5927,12 +6153,13 @@
       <c r="E59" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6877,17 +7104,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="40.19921875" customWidth="1"/>
-    <col min="4" max="5" width="7.59765625" customWidth="1"/>
-    <col min="6" max="6" width="17.09765625" customWidth="1"/>
-    <col min="7" max="7" width="14.8984375" customWidth="1"/>
-    <col min="8" max="26" width="7.59765625" customWidth="1"/>
+    <col min="4" max="6" width="7.59765625" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" customWidth="1"/>
+    <col min="9" max="27" width="7.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6901,22 +7128,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>231</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -6929,17 +7159,18 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>4</v>
       </c>
@@ -6952,17 +7183,18 @@
       <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -6975,23 +7207,24 @@
       <c r="D4" s="1">
         <v>4</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7004,20 +7237,21 @@
       <c r="D5" s="1">
         <v>5</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -7030,20 +7264,21 @@
       <c r="D6" s="1">
         <v>6</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -7056,23 +7291,24 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -7085,20 +7321,21 @@
       <c r="D8" s="1">
         <v>6</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
         <v>3</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -7111,14 +7348,15 @@
       <c r="D9" s="1">
         <v>6</v>
       </c>
-      <c r="E9" s="1">
-        <v>4</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -7131,14 +7369,15 @@
       <c r="D10" s="1">
         <v>6</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>4</v>
       </c>
@@ -7151,20 +7390,21 @@
       <c r="D11" s="1">
         <v>7</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>4</v>
       </c>
@@ -7177,20 +7417,21 @@
       <c r="D12" s="1">
         <v>7</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>4</v>
       </c>
@@ -7203,20 +7444,21 @@
       <c r="D13" s="1">
         <v>7</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
         <v>3</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -7229,20 +7471,21 @@
       <c r="D14" s="1">
         <v>7</v>
       </c>
-      <c r="E14" s="1">
-        <v>4</v>
-      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="1">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -7255,9 +7498,7 @@
       <c r="D15" s="1">
         <v>8</v>
       </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
+      <c r="E15" s="1"/>
       <c r="F15" s="1">
         <v>1</v>
       </c>
@@ -7267,8 +7508,11 @@
       <c r="H15" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>4</v>
       </c>
@@ -7281,20 +7525,21 @@
       <c r="D16" s="1">
         <v>8</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
       <c r="G16" s="1">
         <v>1</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>4</v>
       </c>
@@ -7307,20 +7552,21 @@
       <c r="D17" s="1">
         <v>8</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
         <v>3</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
       <c r="H17" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>4</v>
       </c>
@@ -7333,20 +7579,21 @@
       <c r="D18" s="1">
         <v>8</v>
       </c>
-      <c r="E18" s="1">
-        <v>4</v>
-      </c>
+      <c r="E18" s="1"/>
       <c r="F18" s="1">
+        <v>4</v>
+      </c>
+      <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>4</v>
       </c>
@@ -7359,20 +7606,21 @@
       <c r="D19" s="1">
         <v>9</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
+      <c r="E19" s="1"/>
       <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>4</v>
       </c>
@@ -7385,20 +7633,21 @@
       <c r="D20" s="1">
         <v>9</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -7411,20 +7660,21 @@
       <c r="D21" s="1">
         <v>9</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
         <v>3</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -7437,20 +7687,21 @@
       <c r="D22" s="1">
         <v>9</v>
       </c>
-      <c r="E22" s="1">
-        <v>4</v>
-      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="1">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -7463,20 +7714,21 @@
       <c r="D23" s="1">
         <v>10</v>
       </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
+      <c r="E23" s="1"/>
       <c r="F23" s="1">
         <v>1</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -7489,20 +7741,21 @@
       <c r="D24" s="1">
         <v>10</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -7515,20 +7768,21 @@
       <c r="D25" s="1">
         <v>11</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
+      <c r="E25" s="1"/>
       <c r="F25" s="1">
         <v>1</v>
       </c>
       <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
         <v>2</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -7541,20 +7795,21 @@
       <c r="D26" s="1">
         <v>11</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
       <c r="G26" s="1">
         <v>1</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -7567,17 +7822,18 @@
       <c r="D27" s="1">
         <v>11</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1">
         <v>3</v>
       </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
       <c r="G27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -7590,20 +7846,21 @@
       <c r="D28" s="1">
         <v>11</v>
       </c>
-      <c r="E28" s="1">
-        <v>4</v>
-      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -7616,11 +7873,12 @@
       <c r="D29" s="1">
         <v>12</v>
       </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>4</v>
       </c>
@@ -7633,11 +7891,12 @@
       <c r="D30" s="1">
         <v>12</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -7650,11 +7909,12 @@
       <c r="D31" s="1">
         <v>12</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="1"/>
+      <c r="F31" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -7667,11 +7927,12 @@
       <c r="D32" s="1">
         <v>12</v>
       </c>
-      <c r="E32" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="1"/>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7684,17 +7945,18 @@
       <c r="D33" s="1">
         <v>13</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
+      <c r="E33" s="1"/>
       <c r="F33" s="1">
         <v>1</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7707,17 +7969,18 @@
       <c r="D34" s="1">
         <v>13</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="1"/>
+      <c r="F34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
       <c r="G34" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7730,17 +7993,18 @@
       <c r="D35" s="1">
         <v>13</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="1"/>
+      <c r="F35" s="1">
         <v>3</v>
       </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
       <c r="G35" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7753,17 +8017,18 @@
       <c r="D36" s="1">
         <v>13</v>
       </c>
-      <c r="E36" s="1">
-        <v>4</v>
-      </c>
+      <c r="E36" s="1"/>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7776,11 +8041,12 @@
       <c r="D37" s="1">
         <v>13</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7793,23 +8059,24 @@
       <c r="D38" s="1">
         <v>14</v>
       </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
         <v>0</v>
       </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7822,20 +8089,21 @@
       <c r="D39" s="1">
         <v>14</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="1"/>
+      <c r="F39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>0</v>
       </c>
-      <c r="G39" s="1">
-        <v>1</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7848,20 +8116,21 @@
       <c r="D40" s="1">
         <v>15</v>
       </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
+      <c r="E40" s="1"/>
       <c r="F40" s="1">
         <v>1</v>
       </c>
       <c r="G40" s="1">
         <v>1</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -7874,20 +8143,21 @@
       <c r="D41" s="1">
         <v>15</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="1"/>
+      <c r="F41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>4</v>
       </c>
@@ -7900,20 +8170,21 @@
       <c r="D42" s="1">
         <v>15</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
         <v>3</v>
       </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
       <c r="G42" s="1">
         <v>1</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>4</v>
       </c>
@@ -7926,9 +8197,7 @@
       <c r="D43" s="1">
         <v>16</v>
       </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
+      <c r="E43" s="1"/>
       <c r="F43" s="1">
         <v>1</v>
       </c>
@@ -7938,8 +8207,11 @@
       <c r="H43" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>4</v>
       </c>
@@ -7952,20 +8224,21 @@
       <c r="D44" s="1">
         <v>16</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="1"/>
+      <c r="F44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="1">
-        <v>1</v>
-      </c>
       <c r="G44" s="1">
         <v>1</v>
       </c>
       <c r="H44" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>4</v>
       </c>
@@ -7978,20 +8251,21 @@
       <c r="D45" s="1">
         <v>16</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="1"/>
+      <c r="F45" s="1">
         <v>3</v>
       </c>
-      <c r="F45" s="1">
-        <v>1</v>
-      </c>
       <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
         <v>0.5</v>
       </c>
-      <c r="H45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>4</v>
       </c>
@@ -8004,20 +8278,21 @@
       <c r="D46" s="1">
         <v>16</v>
       </c>
-      <c r="E46" s="1">
-        <v>4</v>
-      </c>
+      <c r="E46" s="1"/>
       <c r="F46" s="1">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G46" s="1">
         <v>0.5</v>
       </c>
       <c r="H46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>4</v>
       </c>
@@ -8030,20 +8305,21 @@
       <c r="D47" s="1">
         <v>16</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="1"/>
+      <c r="F47" s="1">
         <v>5</v>
       </c>
-      <c r="F47" s="1">
+      <c r="G47" s="1">
         <v>0</v>
       </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>4</v>
       </c>
@@ -8056,20 +8332,21 @@
       <c r="D48" s="1">
         <v>16</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="1"/>
+      <c r="F48" s="1">
         <v>6</v>
       </c>
-      <c r="F48" s="1">
+      <c r="G48" s="1">
         <v>0</v>
       </c>
-      <c r="G48" s="1">
-        <v>1</v>
-      </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>4</v>
       </c>
@@ -8082,20 +8359,21 @@
       <c r="D49" s="1">
         <v>17</v>
       </c>
-      <c r="E49" s="1">
-        <v>1</v>
-      </c>
+      <c r="E49" s="1"/>
       <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1">
         <v>0</v>
       </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>4</v>
       </c>
@@ -8108,17 +8386,18 @@
       <c r="D50" s="1">
         <v>17</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <v>0</v>
       </c>
-      <c r="G50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>4</v>
       </c>
@@ -8131,11 +8410,12 @@
       <c r="D51" s="1">
         <v>17</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="1"/>
+      <c r="F51" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>4</v>
       </c>
@@ -8148,11 +8428,12 @@
       <c r="D52" s="1">
         <v>17</v>
       </c>
-      <c r="E52" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="1"/>
+      <c r="F52" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>4</v>
       </c>
@@ -8165,11 +8446,12 @@
       <c r="D53" s="1">
         <v>17</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="1"/>
+      <c r="F53" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>4</v>
       </c>
@@ -8182,11 +8464,12 @@
       <c r="D54" s="1">
         <v>17</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="1"/>
+      <c r="F54" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>4</v>
       </c>
@@ -8199,20 +8482,21 @@
       <c r="D55" s="1">
         <v>18</v>
       </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
+      <c r="E55" s="1"/>
       <c r="F55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>4</v>
       </c>
@@ -8225,20 +8509,21 @@
       <c r="D56" s="1">
         <v>19</v>
       </c>
-      <c r="E56" s="1">
-        <v>1</v>
-      </c>
+      <c r="E56" s="1"/>
       <c r="F56" s="1">
         <v>1</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>4</v>
       </c>
@@ -8251,20 +8536,21 @@
       <c r="D57" s="1">
         <v>19</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="1"/>
+      <c r="F57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="1">
+      <c r="G57" s="1">
         <v>0</v>
       </c>
-      <c r="G57" s="1">
-        <v>1</v>
-      </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>4</v>
       </c>
@@ -8277,20 +8563,21 @@
       <c r="D58" s="1">
         <v>19</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="1"/>
+      <c r="F58" s="1">
         <v>3</v>
       </c>
-      <c r="F58" s="1">
+      <c r="G58" s="1">
         <v>0</v>
       </c>
-      <c r="G58" s="1">
-        <v>1</v>
-      </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>4</v>
       </c>
@@ -8303,20 +8590,21 @@
       <c r="D59" s="1">
         <v>20</v>
       </c>
-      <c r="E59" s="1">
-        <v>1</v>
-      </c>
+      <c r="E59" s="1"/>
       <c r="F59" s="1">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
         <v>0</v>
       </c>
-      <c r="G59" s="1">
-        <v>1</v>
-      </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>4</v>
       </c>
@@ -8329,11 +8617,12 @@
       <c r="D60" s="1">
         <v>20</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="1"/>
+      <c r="F60" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>4</v>
       </c>
@@ -8346,11 +8635,12 @@
       <c r="D61" s="1">
         <v>20</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>4</v>
       </c>
@@ -8363,11 +8653,12 @@
       <c r="D62" s="1">
         <v>20</v>
       </c>
-      <c r="E62" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E62" s="1"/>
+      <c r="F62" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>4</v>
       </c>
@@ -8380,11 +8671,12 @@
       <c r="D63" s="1">
         <v>21</v>
       </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E63" s="1"/>
+      <c r="F63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>4</v>
       </c>
@@ -8397,9 +8689,7 @@
       <c r="D64" s="1">
         <v>22</v>
       </c>
-      <c r="E64" s="1">
-        <v>1</v>
-      </c>
+      <c r="E64" s="1"/>
       <c r="F64" s="1">
         <v>1</v>
       </c>
@@ -8409,8 +8699,11 @@
       <c r="H64" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>4</v>
       </c>
@@ -8423,20 +8716,21 @@
       <c r="D65" s="1">
         <v>22</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="1"/>
+      <c r="F65" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="1">
-        <v>1</v>
-      </c>
       <c r="G65" s="1">
         <v>1</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>4</v>
       </c>
@@ -8449,20 +8743,21 @@
       <c r="D66" s="1">
         <v>22</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="1"/>
+      <c r="F66" s="1">
         <v>3</v>
       </c>
-      <c r="F66" s="1">
-        <v>1</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H66" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>4</v>
       </c>
@@ -8475,20 +8770,21 @@
       <c r="D67" s="1">
         <v>22</v>
       </c>
-      <c r="E67" s="1">
-        <v>4</v>
-      </c>
+      <c r="E67" s="1"/>
       <c r="F67" s="1">
-        <v>1</v>
-      </c>
-      <c r="G67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H67" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>4</v>
       </c>
@@ -8501,9 +8797,7 @@
       <c r="D68" s="1">
         <v>23</v>
       </c>
-      <c r="E68" s="1">
-        <v>1</v>
-      </c>
+      <c r="E68" s="1"/>
       <c r="F68" s="1">
         <v>1</v>
       </c>
@@ -8513,8 +8807,11 @@
       <c r="H68" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>4</v>
       </c>
@@ -8527,20 +8824,21 @@
       <c r="D69" s="1">
         <v>23</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="1"/>
+      <c r="F69" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="1">
-        <v>1</v>
-      </c>
       <c r="G69" s="1">
         <v>1</v>
       </c>
       <c r="H69" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>4</v>
       </c>
@@ -8553,11 +8851,9 @@
       <c r="D70" s="1">
         <v>23</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="1"/>
+      <c r="F70" s="1">
         <v>3</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -8565,8 +8861,11 @@
       <c r="H70" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>4</v>
       </c>
@@ -8579,9 +8878,7 @@
       <c r="D71" s="1">
         <v>24</v>
       </c>
-      <c r="E71" s="1">
-        <v>1</v>
-      </c>
+      <c r="E71" s="1"/>
       <c r="F71" s="1">
         <v>1</v>
       </c>
@@ -8591,8 +8888,11 @@
       <c r="H71" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>4</v>
       </c>
@@ -8605,20 +8905,21 @@
       <c r="D72" s="1">
         <v>24</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="1"/>
+      <c r="F72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="1">
+      <c r="G72" s="1">
         <v>0</v>
       </c>
-      <c r="G72" s="1">
-        <v>1</v>
-      </c>
       <c r="H72" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>4</v>
       </c>
@@ -8631,20 +8932,21 @@
       <c r="D73" s="1">
         <v>24</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="1"/>
+      <c r="F73" s="1">
         <v>3</v>
       </c>
-      <c r="F73" s="1">
+      <c r="G73" s="1">
         <v>0</v>
       </c>
-      <c r="G73" s="1">
-        <v>1</v>
-      </c>
       <c r="H73" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>4</v>
       </c>
@@ -8657,9 +8959,7 @@
       <c r="D74" s="1">
         <v>25</v>
       </c>
-      <c r="E74" s="1">
-        <v>1</v>
-      </c>
+      <c r="E74" s="1"/>
       <c r="F74" s="1">
         <v>1</v>
       </c>
@@ -8669,11 +8969,14 @@
       <c r="H74" s="1">
         <v>1</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>4</v>
       </c>
@@ -8686,20 +8989,21 @@
       <c r="D75" s="1">
         <v>25</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="1"/>
+      <c r="F75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="1">
-        <v>1</v>
-      </c>
       <c r="G75" s="1">
         <v>1</v>
       </c>
       <c r="H75" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>4</v>
       </c>
@@ -8712,20 +9016,21 @@
       <c r="D76" s="1">
         <v>25</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="1"/>
+      <c r="F76" s="1">
         <v>3</v>
       </c>
-      <c r="F76" s="1">
-        <v>1</v>
-      </c>
       <c r="G76" s="1">
         <v>1</v>
       </c>
       <c r="H76" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>4</v>
       </c>
@@ -8738,11 +9043,9 @@
       <c r="D77" s="1">
         <v>25</v>
       </c>
-      <c r="E77" s="1">
-        <v>4</v>
-      </c>
+      <c r="E77" s="1"/>
       <c r="F77" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -8750,8 +9053,11 @@
       <c r="H77" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>4</v>
       </c>
@@ -8764,20 +9070,21 @@
       <c r="D78" s="1">
         <v>26</v>
       </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
+      <c r="E78" s="1"/>
       <c r="F78" s="1">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1">
         <v>0</v>
       </c>
-      <c r="G78" s="1">
-        <v>1</v>
-      </c>
       <c r="H78" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>4</v>
       </c>
@@ -8790,20 +9097,21 @@
       <c r="D79" s="1">
         <v>26</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79" s="1"/>
+      <c r="F79" s="1">
         <v>2</v>
       </c>
-      <c r="F79" s="1">
-        <v>1</v>
-      </c>
       <c r="G79" s="1">
         <v>1</v>
       </c>
       <c r="H79" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>4</v>
       </c>
@@ -8816,17 +9124,18 @@
       <c r="D80" s="1">
         <v>27</v>
       </c>
-      <c r="E80" s="1">
-        <v>1</v>
-      </c>
+      <c r="E80" s="1"/>
       <c r="F80" s="1">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1">
         <v>0</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>4</v>
       </c>
@@ -8839,17 +9148,18 @@
       <c r="D81" s="1">
         <v>27</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81" s="1"/>
+      <c r="F81" s="1">
         <v>2</v>
       </c>
-      <c r="F81" s="1">
+      <c r="G81" s="1">
         <v>0</v>
       </c>
-      <c r="G81" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>4</v>
       </c>
@@ -8862,17 +9172,18 @@
       <c r="D82" s="1">
         <v>27</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82" s="1"/>
+      <c r="F82" s="1">
         <v>3</v>
       </c>
-      <c r="F82" s="1">
+      <c r="G82" s="1">
         <v>0</v>
       </c>
-      <c r="G82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>4</v>
       </c>
@@ -8885,20 +9196,21 @@
       <c r="D83" s="1">
         <v>28</v>
       </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
+      <c r="E83" s="1"/>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
       </c>
-      <c r="I83" s="1" t="s">
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>4</v>
       </c>
@@ -8911,11 +9223,12 @@
       <c r="D84" s="1">
         <v>28</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84" s="1"/>
+      <c r="F84" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>4</v>
       </c>
@@ -8928,11 +9241,12 @@
       <c r="D85" s="1">
         <v>28</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85" s="1"/>
+      <c r="F85" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>4</v>
       </c>
@@ -8945,11 +9259,12 @@
       <c r="D86" s="1">
         <v>29</v>
       </c>
-      <c r="E86" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E86" s="1"/>
+      <c r="F86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>4</v>
       </c>
@@ -8962,11 +9277,12 @@
       <c r="D87" s="1">
         <v>29</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87" s="1"/>
+      <c r="F87" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>4</v>
       </c>
@@ -8979,11 +9295,12 @@
       <c r="D88" s="1">
         <v>29</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88" s="1"/>
+      <c r="F88" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>4</v>
       </c>
@@ -8996,11 +9313,12 @@
       <c r="D89" s="1">
         <v>29</v>
       </c>
-      <c r="E89" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E89" s="1"/>
+      <c r="F89" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>4</v>
       </c>
@@ -9013,11 +9331,12 @@
       <c r="D90" s="1">
         <v>30</v>
       </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E90" s="1"/>
+      <c r="F90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>4</v>
       </c>
@@ -9030,11 +9349,12 @@
       <c r="D91" s="1">
         <v>30</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91" s="1"/>
+      <c r="F91" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>4</v>
       </c>
@@ -9047,11 +9367,12 @@
       <c r="D92" s="1">
         <v>30</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E92" s="1"/>
+      <c r="F92" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>4</v>
       </c>
@@ -9064,11 +9385,12 @@
       <c r="D93" s="1">
         <v>30</v>
       </c>
-      <c r="E93" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E93" s="1"/>
+      <c r="F93" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>4</v>
       </c>
@@ -9081,11 +9403,12 @@
       <c r="D94" s="1">
         <v>30</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E94" s="1"/>
+      <c r="F94" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>4</v>
       </c>
@@ -9098,11 +9421,12 @@
       <c r="D95" s="1">
         <v>30</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E95" s="1"/>
+      <c r="F95" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>4</v>
       </c>
@@ -9115,11 +9439,12 @@
       <c r="D96" s="1">
         <v>31</v>
       </c>
-      <c r="E96" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E96" s="1"/>
+      <c r="F96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>4</v>
       </c>
@@ -9132,11 +9457,12 @@
       <c r="D97" s="1">
         <v>31</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97" s="1"/>
+      <c r="F97" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>4</v>
       </c>
@@ -9149,11 +9475,12 @@
       <c r="D98" s="1">
         <v>31</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="1"/>
+      <c r="F98" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>4</v>
       </c>
@@ -9166,11 +9493,12 @@
       <c r="D99" s="1">
         <v>31</v>
       </c>
-      <c r="E99" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E99" s="1"/>
+      <c r="F99" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>4</v>
       </c>
@@ -9183,11 +9511,12 @@
       <c r="D100" s="1">
         <v>31</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="1"/>
+      <c r="F100" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>4</v>
       </c>
@@ -9200,11 +9529,12 @@
       <c r="D101" s="1">
         <v>32</v>
       </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E101" s="1"/>
+      <c r="F101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>4</v>
       </c>
@@ -9217,11 +9547,12 @@
       <c r="D102" s="1">
         <v>33</v>
       </c>
-      <c r="E102" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E102" s="1"/>
+      <c r="F102" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>4</v>
       </c>
@@ -9234,11 +9565,12 @@
       <c r="D103" s="1">
         <v>33</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="1"/>
+      <c r="F103" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>4</v>
       </c>
@@ -9251,11 +9583,12 @@
       <c r="D104" s="1">
         <v>34</v>
       </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E104" s="1"/>
+      <c r="F104" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>4</v>
       </c>
@@ -9268,11 +9601,12 @@
       <c r="D105" s="1">
         <v>34</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105" s="1"/>
+      <c r="F105" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>4</v>
       </c>
@@ -9285,11 +9619,12 @@
       <c r="D106" s="1">
         <v>34</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106" s="1"/>
+      <c r="F106" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>4</v>
       </c>
@@ -9302,11 +9637,12 @@
       <c r="D107" s="1">
         <v>34</v>
       </c>
-      <c r="E107" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E107" s="1"/>
+      <c r="F107" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>4</v>
       </c>
@@ -9319,11 +9655,12 @@
       <c r="D108" s="1">
         <v>34</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108" s="1"/>
+      <c r="F108" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>4</v>
       </c>
@@ -9336,11 +9673,12 @@
       <c r="D109" s="1">
         <v>34</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E109" s="1"/>
+      <c r="F109" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>4</v>
       </c>
@@ -9353,11 +9691,12 @@
       <c r="D110" s="1">
         <v>35</v>
       </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E110" s="1"/>
+      <c r="F110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>4</v>
       </c>
@@ -9370,11 +9709,12 @@
       <c r="D111" s="1">
         <v>35</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111" s="1"/>
+      <c r="F111" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>4</v>
       </c>
@@ -9387,11 +9727,12 @@
       <c r="D112" s="1">
         <v>35</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112" s="1"/>
+      <c r="F112" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>4</v>
       </c>
@@ -9404,11 +9745,12 @@
       <c r="D113" s="1">
         <v>36</v>
       </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E113" s="1"/>
+      <c r="F113" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>4</v>
       </c>
@@ -9421,11 +9763,12 @@
       <c r="D114" s="1">
         <v>36</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="1"/>
+      <c r="F114" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>4</v>
       </c>
@@ -9438,11 +9781,12 @@
       <c r="D115" s="1">
         <v>36</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="1"/>
+      <c r="F115" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>4</v>
       </c>
@@ -9455,11 +9799,12 @@
       <c r="D116" s="1">
         <v>36</v>
       </c>
-      <c r="E116" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E116" s="1"/>
+      <c r="F116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>4</v>
       </c>
@@ -9472,11 +9817,12 @@
       <c r="D117" s="1">
         <v>36</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="1"/>
+      <c r="F117" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>4</v>
       </c>
@@ -9489,11 +9835,12 @@
       <c r="D118" s="1">
         <v>36</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118" s="1"/>
+      <c r="F118" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>4</v>
       </c>
@@ -9506,11 +9853,12 @@
       <c r="D119" s="1">
         <v>36</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="1"/>
+      <c r="F119" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>4</v>
       </c>
@@ -9523,11 +9871,12 @@
       <c r="D120" s="1">
         <v>36</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120" s="1"/>
+      <c r="F120" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>4</v>
       </c>
@@ -9540,11 +9889,12 @@
       <c r="D121" s="1">
         <v>37</v>
       </c>
-      <c r="E121" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E121" s="1"/>
+      <c r="F121" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>4</v>
       </c>
@@ -9557,11 +9907,12 @@
       <c r="D122" s="1">
         <v>38</v>
       </c>
-      <c r="E122" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="1"/>
+      <c r="F122" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>4</v>
       </c>
@@ -9574,11 +9925,12 @@
       <c r="D123" s="1">
         <v>38</v>
       </c>
-      <c r="E123" s="1">
+      <c r="E123" s="1"/>
+      <c r="F123" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>4</v>
       </c>
@@ -9591,11 +9943,12 @@
       <c r="D124" s="1">
         <v>38</v>
       </c>
-      <c r="E124" s="1">
+      <c r="E124" s="1"/>
+      <c r="F124" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>4</v>
       </c>
@@ -9608,11 +9961,12 @@
       <c r="D125" s="1">
         <v>38</v>
       </c>
-      <c r="E125" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E125" s="1"/>
+      <c r="F125" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>4</v>
       </c>
@@ -9625,11 +9979,12 @@
       <c r="D126" s="1">
         <v>39</v>
       </c>
-      <c r="E126" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E126" s="1"/>
+      <c r="F126" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>4</v>
       </c>
@@ -9642,11 +9997,12 @@
       <c r="D127" s="1">
         <v>40</v>
       </c>
-      <c r="E127" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="1"/>
+      <c r="F127" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>4</v>
       </c>
@@ -9659,11 +10015,12 @@
       <c r="D128" s="1">
         <v>40</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="1"/>
+      <c r="F128" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>4</v>
       </c>
@@ -9676,11 +10033,12 @@
       <c r="D129" s="1">
         <v>40</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="1"/>
+      <c r="F129" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>4</v>
       </c>
@@ -9693,11 +10051,12 @@
       <c r="D130" s="1">
         <v>40</v>
       </c>
-      <c r="E130" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E130" s="1"/>
+      <c r="F130" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>4</v>
       </c>
@@ -9710,23 +10069,24 @@
       <c r="D131" s="1">
         <v>40</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="1"/>
+      <c r="F131" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/data/raw/comparaisons/fiches_excell.xlsx
+++ b/data/raw/comparaisons/fiches_excell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPF\STAGE ACCESS\Code\Prototype_Appli_DefisAccess\data\raw\comparaisons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00077E96-4534-4546-90E1-5CC60BE8BE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE8EA8-0F8E-49F3-8AE4-8F2FD9E84A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="588" yWindow="0" windowWidth="21912" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11976" yWindow="0" windowWidth="11160" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -911,7 +911,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -922,6 +922,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -929,6 +937,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -982,24 +991,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5043,10 +5053,12 @@
   <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.59765625" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="47.59765625" customWidth="1"/>
-    <col min="4" max="6" width="7.59765625" customWidth="1"/>
+    <col min="1" max="1" width="8.296875" customWidth="1"/>
+    <col min="2" max="2" width="26.796875" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" customWidth="1"/>
+    <col min="4" max="4" width="4.19921875" customWidth="1"/>
+    <col min="5" max="5" width="12.19921875" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="13.59765625" customWidth="1"/>
     <col min="8" max="8" width="12.8984375" customWidth="1"/>
     <col min="9" max="27" width="7.59765625" customWidth="1"/>
@@ -5088,7 +5100,7 @@
       <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5148,13 +5160,15 @@
       <c r="E4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="9" t="s">
         <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -5166,7 +5180,9 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="9">
+        <v>2</v>
+      </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
@@ -5184,7 +5200,7 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -5217,7 +5233,9 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -5259,7 +5277,7 @@
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="9" t="s">
         <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -5271,7 +5289,9 @@
       <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="9">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -5295,7 +5315,7 @@
       <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="9" t="s">
         <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -5307,7 +5327,9 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -5385,7 +5407,7 @@
       <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="9" t="s">
         <v>102</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -5397,7 +5419,9 @@
       <c r="E17" s="1">
         <v>4</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="9">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -5457,7 +5481,7 @@
       <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -5469,7 +5493,9 @@
       <c r="E21" s="1">
         <v>4</v>
       </c>
-      <c r="F21" s="1"/>
+      <c r="F21" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -5547,7 +5573,7 @@
       <c r="A26" s="1">
         <v>2</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -5559,7 +5585,9 @@
       <c r="E26" s="1">
         <v>5</v>
       </c>
-      <c r="F26" s="1"/>
+      <c r="F26" s="9">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -5601,7 +5629,7 @@
       <c r="A29" s="1">
         <v>2</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -5613,7 +5641,9 @@
       <c r="E29" s="1">
         <v>3</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -5637,7 +5667,7 @@
       <c r="A31" s="1">
         <v>2</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="9" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -5649,7 +5679,9 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="9">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -5673,7 +5705,7 @@
       <c r="A33" s="1">
         <v>2</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -5685,13 +5717,15 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>2</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="9" t="s">
         <v>114</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -5703,13 +5737,15 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="9" t="s">
         <v>116</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -5757,7 +5793,9 @@
       <c r="E37" s="1">
         <v>3</v>
       </c>
-      <c r="F37" s="1"/>
+      <c r="F37" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -5853,7 +5891,7 @@
       <c r="A43" s="1">
         <v>2</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C43" s="1" t="s">

--- a/data/raw/comparaisons/fiches_excell.xlsx
+++ b/data/raw/comparaisons/fiches_excell.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPF\STAGE ACCESS\Code\Prototype_Appli_DefisAccess\data\raw\comparaisons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c607bc84408f6b/Bureau/defi_access_aloïs/Prototype_Appli_DefisAccess/data/raw/comparaisons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE8EA8-0F8E-49F3-8AE4-8F2FD9E84A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{ABFE8EA8-0F8E-49F3-8AE4-8F2FD9E84A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{549A96DC-40E1-4B66-A2E4-ADB77B241C8C}"/>
   <bookViews>
-    <workbookView xWindow="11976" yWindow="0" windowWidth="11160" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -911,11 +911,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -991,24 +998,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5055,7 +5063,7 @@
   <cols>
     <col min="1" max="1" width="8.296875" customWidth="1"/>
     <col min="2" max="2" width="26.796875" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" customWidth="1"/>
+    <col min="3" max="3" width="50.19921875" customWidth="1"/>
     <col min="4" max="4" width="4.19921875" customWidth="1"/>
     <col min="5" max="5" width="12.19921875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5903,7 +5911,9 @@
       <c r="E43" s="1">
         <v>6</v>
       </c>
-      <c r="F43" s="1"/>
+      <c r="F43" s="10">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
@@ -5975,7 +5985,9 @@
       <c r="E47" s="1">
         <v>4</v>
       </c>
-      <c r="F47" s="1"/>
+      <c r="F47" s="10">
+        <v>4</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
@@ -6029,7 +6041,9 @@
       <c r="E50" s="1">
         <v>3</v>
       </c>
-      <c r="F50" s="1"/>
+      <c r="F50" s="10">
+        <v>3</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
@@ -6065,7 +6079,9 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="1"/>
+      <c r="F52" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">

--- a/data/raw/comparaisons/fiches_excell.xlsx
+++ b/data/raw/comparaisons/fiches_excell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c607bc84408f6b/Bureau/defi_access_aloïs/Prototype_Appli_DefisAccess/data/raw/comparaisons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{ABFE8EA8-0F8E-49F3-8AE4-8F2FD9E84A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{549A96DC-40E1-4B66-A2E4-ADB77B241C8C}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{ABFE8EA8-0F8E-49F3-8AE4-8F2FD9E84A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C6A12D3-884A-4B55-852B-87EAE8F34560}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6117,7 +6117,9 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="1"/>
+      <c r="F54" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
@@ -6189,7 +6191,7 @@
       <c r="E58" s="1">
         <v>4</v>
       </c>
-      <c r="F58" s="1"/>
+      <c r="F58" s="10"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
@@ -6207,7 +6209,9 @@
       <c r="E59" s="1">
         <v>5</v>
       </c>
-      <c r="F59" s="1"/>
+      <c r="F59" s="10">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
